--- a/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
+++ b/VerveStacks_POL_grids_kan10/SuppXLS/Scen_TSParameters_ts_12t.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan10\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6947E20D-EF43-41DD-8791-8F8596683DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9BA1CBAF-97CA-4FB0-82FB-F9D234943D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -573,10 +573,10 @@
     <t>day_night</t>
   </si>
   <si>
-    <t>SaD,RaD,FaD,FaP,SaP,WaD,RaP,WaP</t>
-  </si>
-  <si>
-    <t>FaP,SaP,FaN,SaN,WaN,WaP,RaP,RaN</t>
+    <t>SaD,FaP,SaP,WaP,WaD,RaP,RaD,FaD</t>
+  </si>
+  <si>
+    <t>FaP,SaP,SaN,WaN,RaN,WaP,FaN,RaP</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1171,7 +1171,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>FaP,SaP,FaN,SaN,WaN,WaP,RaP,RaN</v>
+        <v>FaP,SaP,SaN,WaN,RaN,WaP,FaN,RaP</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>SaD,RaD,FaD,FaP,SaP,WaD,RaP,WaP</v>
+        <v>SaD,FaP,SaP,WaP,WaD,RaP,RaD,FaD</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1299,7 +1299,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6B5C091-1E84-487B-80CD-9F73FA4EBFB7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C17D626A-057D-4C51-80CE-99E638312A3D}">
   <dimension ref="A9:G14"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1383,7 +1383,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B709F0AB-CC00-41F1-B4E4-695529FC2439}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABE59EA7-1A35-4864-99BC-2AA4E6F3E14B}">
   <dimension ref="B9:O250"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -9125,7 +9125,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4E91120-E656-43EA-A09C-7A9402988DAF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA4D0AC-8E9B-4B78-8F55-3409A69BEF35}">
   <dimension ref="B9:BL60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14338,7 +14338,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77CBE639-3604-4C93-8E19-AF7B06BD99DA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2992BC7-6ADD-4843-AF5E-A5FF405D54C8}">
   <dimension ref="B9:E22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14536,7 +14536,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A8664DF-DFD1-42CB-83D3-63F6BFB20ACA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F7B54C2-2366-402A-A725-FA8DCB875B34}">
   <dimension ref="B9:D34"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14827,7 +14827,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F6A6289-6943-411A-9563-3A038CBB47E8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB003031-3238-4CD8-A747-20B046CC4024}">
   <dimension ref="B9:D22"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14986,7 +14986,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72FEE966-A0EF-4A8F-B4D5-7042028145B0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{725C1D01-21E6-4255-9591-98F4B2C7E720}">
   <dimension ref="B9:E126"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -15116,7 +15116,7 @@
         <v>45</v>
       </c>
       <c r="D18">
-        <v>0.20653333333333332</v>
+        <v>0.20653333333333335</v>
       </c>
       <c r="E18" t="s">
         <v>184</v>
@@ -15158,7 +15158,7 @@
         <v>43</v>
       </c>
       <c r="D21">
-        <v>0.12036666666666668</v>
+        <v>0.12036666666666666</v>
       </c>
       <c r="E21" t="s">
         <v>184</v>
@@ -15214,7 +15214,7 @@
         <v>43</v>
       </c>
       <c r="D25">
-        <v>0.2446666666666667</v>
+        <v>0.24466666666666667</v>
       </c>
       <c r="E25" t="s">
         <v>184</v>
@@ -15564,7 +15564,7 @@
         <v>45</v>
       </c>
       <c r="D50">
-        <v>0.30259999999999998</v>
+        <v>0.30260000000000004</v>
       </c>
       <c r="E50" t="s">
         <v>184</v>
@@ -15662,7 +15662,7 @@
         <v>43</v>
       </c>
       <c r="D57">
-        <v>0.18733333333333335</v>
+        <v>0.18733333333333332</v>
       </c>
       <c r="E57" t="s">
         <v>184</v>
@@ -15732,7 +15732,7 @@
         <v>45</v>
       </c>
       <c r="D62">
-        <v>0.29860000000000003</v>
+        <v>0.29859999999999998</v>
       </c>
       <c r="E62" t="s">
         <v>184</v>
@@ -15774,7 +15774,7 @@
         <v>43</v>
       </c>
       <c r="D65">
-        <v>0.20076666666666665</v>
+        <v>0.20076666666666668</v>
       </c>
       <c r="E65" t="s">
         <v>184</v>
@@ -15844,7 +15844,7 @@
         <v>45</v>
       </c>
       <c r="D70">
-        <v>0.37280000000000002</v>
+        <v>0.37279999999999996</v>
       </c>
       <c r="E70" t="s">
         <v>184</v>
@@ -16012,7 +16012,7 @@
         <v>45</v>
       </c>
       <c r="D82">
-        <v>0.3242666666666667</v>
+        <v>0.32426666666666665</v>
       </c>
       <c r="E82" t="s">
         <v>184</v>
@@ -16068,7 +16068,7 @@
         <v>45</v>
       </c>
       <c r="D86">
-        <v>0.30743333333333334</v>
+        <v>0.30743333333333328</v>
       </c>
       <c r="E86" t="s">
         <v>184</v>
@@ -16180,7 +16180,7 @@
         <v>45</v>
       </c>
       <c r="D94">
-        <v>0.3143333333333333</v>
+        <v>0.31433333333333335</v>
       </c>
       <c r="E94" t="s">
         <v>184</v>
@@ -16334,7 +16334,7 @@
         <v>43</v>
       </c>
       <c r="D105">
-        <v>0.19526666666666667</v>
+        <v>0.1952666666666667</v>
       </c>
       <c r="E105" t="s">
         <v>184</v>
@@ -16460,7 +16460,7 @@
         <v>45</v>
       </c>
       <c r="D114">
-        <v>0.31429999999999997</v>
+        <v>0.31430000000000002</v>
       </c>
       <c r="E114" t="s">
         <v>184</v>
@@ -16572,7 +16572,7 @@
         <v>45</v>
       </c>
       <c r="D122">
-        <v>0.31936666666666663</v>
+        <v>0.31936666666666669</v>
       </c>
       <c r="E122" t="s">
         <v>184</v>
